--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92554223384</v>
+        <v>46157.93109531989</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93109531989</v>
+        <v>46157.93133973162</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93133973162</v>
+        <v>46157.93381579958</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93381579958</v>
+        <v>46157.93693153558</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93693153558</v>
+        <v>46158.28203922432</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28203922432</v>
+        <v>46158.29650647467</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29650647467</v>
+        <v>46158.29805357679</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29805357679</v>
+        <v>46158.33368505531</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33368505531</v>
+        <v>46158.37220383128</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37220383128</v>
+        <v>46158.372744993</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
